--- a/04.DataAnalysis/00.rawdata/InVitro/17GUSformat.xlsx
+++ b/04.DataAnalysis/00.rawdata/InVitro/17GUSformat.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13060" activeTab="1"/>
+    <workbookView windowWidth="29100" windowHeight="13040"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525"/>
@@ -15,10 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="26">
-  <si>
-    <t>Time</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="25">
   <si>
     <t>Dot1</t>
   </si>
@@ -30,9 +27,6 @@
   </si>
   <si>
     <t>GUS</t>
-  </si>
-  <si>
-    <t>CC</t>
   </si>
   <si>
     <t>Sub</t>
@@ -94,19 +88,21 @@
   <si>
     <t>PNPG</t>
   </si>
+  <si>
+    <t>Time</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,17 +112,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial Regular"/>
       <charset val="134"/>
     </font>
@@ -595,137 +580,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -733,24 +718,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1277,15 +1246,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="3" width="14.7142857142857"/>
-    <col min="4" max="4" width="10.4821428571429" customWidth="1"/>
-    <col min="5" max="5" width="14.4196428571429" customWidth="1"/>
+    <col min="1" max="3" width="12.7857142857143"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1301,793 +1268,583 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3">
+        <v>27.2148732341071</v>
+      </c>
+      <c r="B2" s="3">
+        <v>32.3803416238912</v>
+      </c>
+      <c r="C2" s="3">
+        <v>30.0705900323345</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="4">
-        <v>180</v>
-      </c>
-      <c r="B2" s="5">
-        <v>18.4018808347062</v>
-      </c>
-      <c r="C2" s="5">
-        <v>21.8946155958265</v>
-      </c>
-      <c r="D2" s="5">
-        <v>20.3328308621636</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3">
+        <v>7.85741256396555</v>
+      </c>
+      <c r="B3" s="3">
+        <v>31.7327227685238</v>
+      </c>
+      <c r="C3" s="3">
+        <v>33.5977706343106</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3">
+        <v>593.364279768002</v>
+      </c>
+      <c r="B4" s="3">
+        <v>611.819882679462</v>
+      </c>
+      <c r="C4" s="3">
+        <v>606.924247780921</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3">
-        <v>180</v>
-      </c>
-      <c r="B3" s="5">
-        <v>8.36790865824639</v>
-      </c>
-      <c r="C3" s="5">
-        <v>33.7943977667948</v>
-      </c>
-      <c r="D3" s="5">
-        <v>35.7806177924218</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3">
+        <v>2514.95746274108</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2514.05533911031</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2101.48452968338</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>45.4308756872425</v>
+      </c>
+      <c r="B6" s="3">
+        <v>45.7434352568239</v>
+      </c>
+      <c r="C6" s="3">
+        <v>34.1617542535942</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>0.422085559700239</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.39889773834728</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.372013307793124</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>84.5701768356231</v>
+      </c>
+      <c r="B8" s="3">
+        <v>91.7264174930079</v>
+      </c>
+      <c r="C8" s="3">
+        <v>91.3440792616994</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>1.3572835066992</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1.59485895295578</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.56146997131972</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>6195.91739852837</v>
+      </c>
+      <c r="B10" s="3">
+        <v>4416.72600680434</v>
+      </c>
+      <c r="C10" s="3">
+        <v>5667.71105308964</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>3.51067887109077</v>
+      </c>
+      <c r="B11" s="3">
+        <v>3.79481311975591</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3.96526433139705</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>0.0297358682750321</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.116479174624297</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.113932732865938</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>23.1665699221206</v>
+      </c>
+      <c r="B13" s="3">
+        <v>26.0603202244473</v>
+      </c>
+      <c r="C13" s="3">
+        <v>22.7579451458424</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
+        <v>10.6967408029095</v>
+      </c>
+      <c r="B14" s="3">
+        <v>10.3957196810743</v>
+      </c>
+      <c r="C14" s="3">
+        <v>9.07917191215555</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>4446.37269595856</v>
+      </c>
+      <c r="B15" s="3">
+        <v>4311.11461702295</v>
+      </c>
+      <c r="C15" s="3">
+        <v>4210.10228497804</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>1836.66953352173</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1821.05090715485</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1912.61334316255</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>65.2837561724094</v>
+      </c>
+      <c r="B17" s="3">
+        <v>66.1724432193902</v>
+      </c>
+      <c r="C17" s="3">
+        <v>62.9851145009546</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>4.8443893585912</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4.74911932361282</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3.21570582740841</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>22.5660137812407</v>
+      </c>
+      <c r="B19" s="3">
+        <v>23.0711211677537</v>
+      </c>
+      <c r="C19" s="3">
+        <v>22.8526963519643</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>1.64685029047405</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1.66418555668957</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1.62084739115078</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>88.1020247536085</v>
+      </c>
+      <c r="B21" s="3">
+        <v>87.3118158186032</v>
+      </c>
+      <c r="C21" s="3">
+        <v>87.3996168113815</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3">
+      <c r="E21" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>569.286924781645</v>
+      </c>
+      <c r="B22" s="3">
+        <v>590.926867422761</v>
+      </c>
+      <c r="C22" s="3">
+        <v>524.833789597184</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>25.6567698542401</v>
+      </c>
+      <c r="B23" s="3">
+        <v>23.4903661159341</v>
+      </c>
+      <c r="C23" s="3">
+        <v>21.9285401650623</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>49.0339527954207</v>
+      </c>
+      <c r="B24" s="3">
+        <v>49.1997401171713</v>
+      </c>
+      <c r="C24" s="3">
+        <v>48.7142521087475</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>234.62424176383</v>
+      </c>
+      <c r="B25" s="3">
+        <v>202.061675928953</v>
+      </c>
+      <c r="C25" s="3">
+        <v>195.456757836621</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>69.4262874020804</v>
+      </c>
+      <c r="B26" s="3">
+        <v>67.3898805701811</v>
+      </c>
+      <c r="C26" s="3">
+        <v>66.8581182312401</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>6.15761957798511</v>
+      </c>
+      <c r="B27" s="3">
+        <v>6.96829715106478</v>
+      </c>
+      <c r="C27" s="3">
+        <v>6.31196479760448</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>127.931115413953</v>
+      </c>
+      <c r="B28" s="3">
+        <v>131.280877779734</v>
+      </c>
+      <c r="C28" s="3">
+        <v>123.263363257642</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6">
-        <v>36.3895478674721</v>
-      </c>
-      <c r="C4" s="6">
-        <v>37.5213838550247</v>
-      </c>
-      <c r="D4" s="6">
-        <v>37.2211468057844</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3">
-        <v>15</v>
-      </c>
-      <c r="B5" s="6">
-        <v>19.2922386966868</v>
-      </c>
-      <c r="C5" s="6">
-        <v>19.2853185063152</v>
-      </c>
-      <c r="D5" s="6">
-        <v>16.1204878272012</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3">
-        <v>180</v>
-      </c>
-      <c r="B6" s="5">
-        <v>33.2949258649094</v>
-      </c>
-      <c r="C6" s="5">
-        <v>33.5239913966685</v>
-      </c>
-      <c r="D6" s="5">
-        <v>25.0361248398316</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="3">
-        <v>195</v>
-      </c>
-      <c r="B7" s="7">
-        <v>0.3768</v>
-      </c>
-      <c r="C7" s="7">
-        <v>0.3561</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0.3321</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3">
-        <v>195</v>
-      </c>
-      <c r="B8" s="7">
-        <v>75.6698</v>
-      </c>
-      <c r="C8" s="7">
-        <v>82.0729</v>
-      </c>
-      <c r="D8" s="7">
-        <v>81.7308</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3">
-        <v>195</v>
-      </c>
-      <c r="B9" s="7">
-        <v>1.2683</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1.4903</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.4591</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3">
-        <v>15</v>
-      </c>
-      <c r="B10" s="8">
-        <v>39.1551</v>
-      </c>
-      <c r="C10" s="8">
-        <v>27.9115</v>
-      </c>
-      <c r="D10" s="8">
-        <v>35.8171</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="E28" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>979.635858828555</v>
+      </c>
+      <c r="B29" s="3">
+        <v>990.021891184794</v>
+      </c>
+      <c r="C29" s="3">
+        <v>998.602167761226</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3">
-        <v>195</v>
-      </c>
-      <c r="B11" s="7">
-        <v>2.3933</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2.587</v>
-      </c>
-      <c r="D11" s="7">
-        <v>2.7032</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="E29" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>63.8529724761767</v>
+      </c>
+      <c r="B30" s="3">
+        <v>71.8874860929715</v>
+      </c>
+      <c r="C30" s="3">
+        <v>69.6852174333672</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="3">
-        <v>195</v>
-      </c>
-      <c r="B12" s="7">
-        <v>0.0362</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.1418</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.1387</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="E30" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>3.03293048999587</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2.32923794538739</v>
+      </c>
+      <c r="C31" s="3">
+        <v>2.27288451452356</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3">
+        <v>1324.97696277184</v>
+      </c>
+      <c r="B32" s="3">
+        <v>1389.28461727485</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1486.71366261211</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3">
+        <v>5.28512146220917</v>
+      </c>
+      <c r="B33" s="3">
+        <v>6.35834848696788</v>
+      </c>
+      <c r="C33" s="3">
+        <v>5.5937893411666</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="3">
-        <v>180</v>
-      </c>
-      <c r="B13" s="7">
-        <v>19.1569</v>
-      </c>
-      <c r="C13" s="7">
-        <v>21.5498</v>
-      </c>
-      <c r="D13" s="7">
-        <v>18.819</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="E33" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3">
+        <v>165.292513999411</v>
+      </c>
+      <c r="B34" s="3">
+        <v>138.807839669909</v>
+      </c>
+      <c r="C34" s="3">
+        <v>125.101311523725</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3">
+        <v>2148.29021061765</v>
+      </c>
+      <c r="B35" s="3">
+        <v>2137.09868265363</v>
+      </c>
+      <c r="C35" s="3">
+        <v>2015.2244221819</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="3">
-        <v>150</v>
-      </c>
-      <c r="B14" s="7">
-        <v>7.6471</v>
-      </c>
-      <c r="C14" s="7">
-        <v>7.4319</v>
-      </c>
-      <c r="D14" s="7">
-        <v>6.4907</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3">
-        <v>15</v>
-      </c>
-      <c r="B15" s="8">
-        <v>42.275</v>
-      </c>
-      <c r="C15" s="8">
-        <v>40.989</v>
-      </c>
-      <c r="D15" s="8">
-        <v>40.0286</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8">
-        <v>112.1149</v>
-      </c>
-      <c r="C16" s="8">
-        <v>111.1615</v>
-      </c>
-      <c r="D16" s="8">
-        <v>116.7507</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3">
-        <v>180</v>
-      </c>
-      <c r="B17" s="5">
-        <v>39.8714012447373</v>
-      </c>
-      <c r="C17" s="5">
-        <v>40.4141579718104</v>
-      </c>
-      <c r="D17" s="5">
-        <v>38.467528830313</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3">
-        <v>180</v>
-      </c>
-      <c r="B18" s="5">
-        <v>4.34120263591433</v>
-      </c>
-      <c r="C18" s="5">
-        <v>4.25582829946916</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.8816904631155</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="4">
-        <v>195</v>
-      </c>
-      <c r="B19" s="7">
-        <v>16.53</v>
-      </c>
-      <c r="C19" s="7">
-        <v>16.9</v>
-      </c>
-      <c r="D19" s="7">
-        <v>16.74</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="4">
-        <v>195</v>
-      </c>
-      <c r="B20" s="7">
-        <v>1.9</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1.92</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1.87</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="4">
-        <v>195</v>
-      </c>
-      <c r="B21" s="7">
-        <v>70.24</v>
-      </c>
-      <c r="C21" s="7">
-        <v>69.61</v>
-      </c>
-      <c r="D21" s="7">
-        <v>69.68</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="4">
-        <v>15</v>
-      </c>
-      <c r="B22" s="8">
-        <v>43.67</v>
-      </c>
-      <c r="C22" s="8">
-        <v>45.33</v>
-      </c>
-      <c r="D22" s="8">
-        <v>40.26</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4">
-        <v>195</v>
-      </c>
-      <c r="B23" s="7">
-        <v>20.37</v>
-      </c>
-      <c r="C23" s="7">
-        <v>18.65</v>
-      </c>
-      <c r="D23" s="7">
-        <v>17.41</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4">
-        <v>195</v>
-      </c>
-      <c r="B24" s="7">
-        <v>43.7731</v>
-      </c>
-      <c r="C24" s="7">
-        <v>43.9211</v>
-      </c>
-      <c r="D24" s="7">
-        <v>43.4877</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="4">
-        <v>15</v>
-      </c>
-      <c r="B25" s="8">
-        <v>16.1486</v>
-      </c>
-      <c r="C25" s="8">
-        <v>13.9074</v>
-      </c>
-      <c r="D25" s="8">
-        <v>13.4528</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="4">
-        <v>195</v>
-      </c>
-      <c r="B26" s="7">
-        <v>64.8747</v>
-      </c>
-      <c r="C26" s="7">
-        <v>62.9718</v>
-      </c>
-      <c r="D26" s="7">
-        <v>62.4749</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="4">
-        <v>195</v>
-      </c>
-      <c r="B27" s="7">
-        <v>5.0587</v>
-      </c>
-      <c r="C27" s="7">
-        <v>5.7247</v>
-      </c>
-      <c r="D27" s="7">
-        <v>5.1855</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="4">
-        <v>195</v>
-      </c>
-      <c r="B28" s="7">
-        <v>87.2132</v>
-      </c>
-      <c r="C28" s="7">
-        <v>89.4968</v>
-      </c>
-      <c r="D28" s="7">
-        <v>84.0311</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3">
-        <v>15</v>
-      </c>
-      <c r="B29" s="7">
-        <v>91.738</v>
-      </c>
-      <c r="C29" s="7">
-        <v>92.7106</v>
-      </c>
-      <c r="D29" s="7">
-        <v>93.5141</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="3">
-        <v>180</v>
-      </c>
-      <c r="B30" s="7">
-        <v>52.8013</v>
-      </c>
-      <c r="C30" s="7">
-        <v>59.4452</v>
-      </c>
-      <c r="D30" s="7">
-        <v>57.6241</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="3">
-        <v>180</v>
-      </c>
-      <c r="B31" s="7">
-        <v>2.7179</v>
-      </c>
-      <c r="C31" s="7">
-        <v>2.0873</v>
-      </c>
-      <c r="D31" s="7">
-        <v>2.0368</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="3">
-        <v>16</v>
-      </c>
-      <c r="B32" s="8">
-        <v>86.2719</v>
-      </c>
-      <c r="C32" s="8">
-        <v>90.4591</v>
-      </c>
-      <c r="D32" s="8">
-        <v>96.8029</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="3">
-        <v>180</v>
-      </c>
-      <c r="B33" s="7">
-        <v>4.534</v>
-      </c>
-      <c r="C33" s="7">
-        <v>5.4547</v>
-      </c>
-      <c r="D33" s="7">
-        <v>4.7988</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="3">
-        <v>16</v>
-      </c>
-      <c r="B34" s="8">
-        <v>8.9734</v>
-      </c>
-      <c r="C34" s="8">
-        <v>7.5356</v>
-      </c>
-      <c r="D34" s="8">
-        <v>6.7915</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="3">
-        <v>16</v>
-      </c>
-      <c r="B35" s="8">
-        <v>21.7871</v>
-      </c>
-      <c r="C35" s="8">
-        <v>21.6736</v>
-      </c>
-      <c r="D35" s="8">
-        <v>20.4376</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>25</v>
+      <c r="E35" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2107,22 +1864,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2139,10 +1896,10 @@
         <v>0.545633351638294</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2159,10 +1916,10 @@
         <v>2.37479956068094</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2179,10 +1936,10 @@
         <v>4.03537799743731</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2199,10 +1956,10 @@
         <v>7.57136280431997</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2219,10 +1976,10 @@
         <v>11.1129306241992</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2239,10 +1996,10 @@
         <v>14.4477201171518</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2259,10 +2016,10 @@
         <v>17.8946549514919</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2279,10 +2036,10 @@
         <v>20.3328308621636</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2299,10 +2056,10 @@
         <v>21.7059353834889</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2319,10 +2076,10 @@
         <v>24.0300448471536</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2339,10 +2096,10 @@
         <v>29.5726267618525</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2360,10 +2117,10 @@
         <v>1.12213435841113</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2381,10 +2138,10 @@
         <v>4.42684239428885</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2402,10 +2159,10 @@
         <v>7.44300109829764</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2423,10 +2180,10 @@
         <v>13.7921911037891</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2444,10 +2201,10 @@
         <v>20.0599762035512</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2465,10 +2222,10 @@
         <v>25.9263820245286</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2486,10 +2243,10 @@
         <v>31.5322405271829</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2507,10 +2264,10 @@
         <v>35.7806177924218</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2528,10 +2285,10 @@
         <v>37.9538531942156</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2549,10 +2306,10 @@
         <v>41.5337314662273</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2570,10 +2327,10 @@
         <v>49.4214177192019</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2590,10 +2347,10 @@
         <v>11.1350777960827</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2610,10 +2367,10 @@
         <v>37.2211468057844</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2630,10 +2387,10 @@
         <v>52.6913664653121</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2650,10 +2407,10 @@
         <v>72.6327942522424</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2670,10 +2427,10 @@
         <v>82.1833781804869</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2690,10 +2447,10 @@
         <v>86.2148462383306</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2710,10 +2467,10 @@
         <v>88.1741634632986</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2730,10 +2487,10 @@
         <v>91.0561220940875</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2750,10 +2507,10 @@
         <v>87.0719540545488</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2770,10 +2527,10 @@
         <v>87.9362557203002</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2790,10 +2547,10 @@
         <v>88.8864689730917</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2810,10 +2567,10 @@
         <v>-0.321512904997254</v>
       </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2830,10 +2587,10 @@
         <v>-0.166129416071755</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2850,10 +2607,10 @@
         <v>-0.0614259564341936</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2870,10 +2627,10 @@
         <v>0.217627677100494</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2890,10 +2647,10 @@
         <v>0.516968698517298</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2910,10 +2667,10 @@
         <v>0.805990298370859</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2930,10 +2687,10 @@
         <v>1.15961010433828</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2950,10 +2707,10 @@
         <v>1.37767801574227</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2970,10 +2727,10 @@
         <v>1.53524345597657</v>
       </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2990,10 +2747,10 @@
         <v>1.79561504667765</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -3010,10 +2767,10 @@
         <v>2.44726340838367</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -3030,10 +2787,10 @@
         <v>56.4980468606992</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -3050,10 +2807,10 @@
         <v>110.829190005491</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -3070,10 +2827,10 @@
         <v>117.917314662273</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -3090,10 +2847,10 @@
         <v>120.99438586857</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3110,10 +2867,10 @@
         <v>119.687267984624</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -3130,10 +2887,10 @@
         <v>118.376433278418</v>
       </c>
       <c r="E51" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -3150,10 +2907,10 @@
         <v>118.582835438404</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -3170,10 +2927,10 @@
         <v>119.615364268717</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3190,10 +2947,10 @@
         <v>114.413694856306</v>
       </c>
       <c r="E54" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -3210,10 +2967,10 @@
         <v>114.83779059125</v>
       </c>
       <c r="E55" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -3230,10 +2987,10 @@
         <v>113.880155592165</v>
       </c>
       <c r="E56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -3250,10 +3007,10 @@
         <v>0.00380743181402167</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -3270,10 +3027,10 @@
         <v>1.91728720483251</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3290,10 +3047,10 @@
         <v>4.42108639941424</v>
       </c>
       <c r="E59" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -3310,10 +3067,10 @@
         <v>9.50819787662457</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -3330,10 +3087,10 @@
         <v>14.7360269082922</v>
       </c>
       <c r="E61" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -3350,10 +3107,10 @@
         <v>17.7525022881201</v>
       </c>
       <c r="E62" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -3370,10 +3127,10 @@
         <v>21.6972423576789</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -3390,10 +3147,10 @@
         <v>25.0361248398316</v>
       </c>
       <c r="E64" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3410,10 +3167,10 @@
         <v>27.208522789676</v>
       </c>
       <c r="E65" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3430,10 +3187,10 @@
         <v>30.4206791140399</v>
       </c>
       <c r="E66" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -3450,10 +3207,10 @@
         <v>37.516364634816</v>
       </c>
       <c r="E67" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3470,10 +3227,10 @@
         <v>-0.3429</v>
       </c>
       <c r="E68" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -3490,10 +3247,10 @@
         <v>-0.3005</v>
       </c>
       <c r="E69" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3510,10 +3267,10 @@
         <v>-0.2264</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3530,10 +3287,10 @@
         <v>-0.1158</v>
       </c>
       <c r="E71" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3550,10 +3307,10 @@
         <v>0.1036</v>
       </c>
       <c r="E72" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3570,10 +3327,10 @@
         <v>0.3321</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3590,10 +3347,10 @@
         <v>0.6324</v>
       </c>
       <c r="E74" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3610,10 +3367,10 @@
         <v>0.8287</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3630,10 +3387,10 @@
         <v>2.6298</v>
       </c>
       <c r="E76" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3650,10 +3407,10 @@
         <v>14.4651</v>
       </c>
       <c r="E77" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3670,10 +3427,10 @@
         <v>26.2144</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3690,10 +3447,10 @@
         <v>47.6746</v>
       </c>
       <c r="E79" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3710,10 +3467,10 @@
         <v>69.1554</v>
       </c>
       <c r="E80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3730,10 +3487,10 @@
         <v>81.7308</v>
       </c>
       <c r="E81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3750,10 +3507,10 @@
         <v>91.8118</v>
       </c>
       <c r="E82" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3770,10 +3527,10 @@
         <v>95.8945</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3790,10 +3547,10 @@
         <v>-0.3118</v>
       </c>
       <c r="E84" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3810,10 +3567,10 @@
         <v>-0.1744</v>
       </c>
       <c r="E85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3830,10 +3587,10 @@
         <v>-0.0162</v>
       </c>
       <c r="E86" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3850,10 +3607,10 @@
         <v>0.3094</v>
       </c>
       <c r="E87" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3870,10 +3627,10 @@
         <v>0.8794</v>
       </c>
       <c r="E88" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3890,10 +3647,10 @@
         <v>1.4591</v>
       </c>
       <c r="E89" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3910,10 +3667,10 @@
         <v>2.1902</v>
       </c>
       <c r="E90" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3930,10 +3687,10 @@
         <v>2.6905</v>
       </c>
       <c r="E91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3950,10 +3707,10 @@
         <v>91.701</v>
       </c>
       <c r="E92" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3970,10 +3727,10 @@
         <v>109.7922</v>
       </c>
       <c r="E93" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3990,10 +3747,10 @@
         <v>110.4612</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4010,10 +3767,10 @@
         <v>113.5988</v>
       </c>
       <c r="E95" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -4030,10 +3787,10 @@
         <v>113.3743</v>
       </c>
       <c r="E96" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -4050,10 +3807,10 @@
         <v>114.3052</v>
       </c>
       <c r="E97" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -4070,10 +3827,10 @@
         <v>115.4176</v>
       </c>
       <c r="E98" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -4090,10 +3847,10 @@
         <v>114.6784</v>
       </c>
       <c r="E99" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -4110,10 +3867,10 @@
         <v>-0.3272</v>
       </c>
       <c r="E100" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -4130,10 +3887,10 @@
         <v>-0.1092</v>
       </c>
       <c r="E101" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -4150,10 +3907,10 @@
         <v>0.1516</v>
       </c>
       <c r="E102" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -4170,10 +3927,10 @@
         <v>0.7553</v>
       </c>
       <c r="E103" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -4190,10 +3947,10 @@
         <v>1.7798</v>
       </c>
       <c r="E104" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -4210,10 +3967,10 @@
         <v>2.7032</v>
       </c>
       <c r="E105" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -4230,10 +3987,10 @@
         <v>3.8356</v>
       </c>
       <c r="E106" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -4250,10 +4007,10 @@
         <v>4.5973</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -4270,10 +4027,10 @@
         <v>-0.3611</v>
       </c>
       <c r="E108" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -4290,10 +4047,10 @@
         <v>-0.3404</v>
       </c>
       <c r="E109" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -4310,10 +4067,10 @@
         <v>-0.2816</v>
       </c>
       <c r="E110" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -4330,10 +4087,10 @@
         <v>-0.1797</v>
       </c>
       <c r="E111" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -4350,10 +4107,10 @@
         <v>-0.0216</v>
       </c>
       <c r="E112" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -4370,10 +4127,10 @@
         <v>0.1387</v>
       </c>
       <c r="E113" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4390,10 +4147,10 @@
         <v>0.3379</v>
       </c>
       <c r="E114" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4410,10 +4167,10 @@
         <v>0.4609</v>
       </c>
       <c r="E115" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4430,10 +4187,10 @@
         <v>91.701</v>
       </c>
       <c r="E116" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4450,10 +4207,10 @@
         <v>109.7922</v>
       </c>
       <c r="E117" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4470,10 +4227,10 @@
         <v>110.4612</v>
       </c>
       <c r="E118" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4490,10 +4247,10 @@
         <v>113.5988</v>
       </c>
       <c r="E119" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4510,10 +4267,10 @@
         <v>113.3743</v>
       </c>
       <c r="E120" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4530,10 +4287,10 @@
         <v>114.3052</v>
       </c>
       <c r="E121" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4550,10 +4307,10 @@
         <v>115.4176</v>
       </c>
       <c r="E122" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4570,10 +4327,10 @@
         <v>114.6784</v>
       </c>
       <c r="E123" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4590,10 +4347,10 @@
         <v>2.3202</v>
       </c>
       <c r="E124" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4610,10 +4367,10 @@
         <v>3.4118</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4630,10 +4387,10 @@
         <v>4.8362</v>
       </c>
       <c r="E126" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4650,10 +4407,10 @@
         <v>8.2015</v>
       </c>
       <c r="E127" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4670,10 +4427,10 @@
         <v>13.455</v>
       </c>
       <c r="E128" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4690,10 +4447,10 @@
         <v>18.819</v>
       </c>
       <c r="E129" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4710,10 +4467,10 @@
         <v>24.2039</v>
       </c>
       <c r="E130" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4730,10 +4487,10 @@
         <v>28.6276</v>
       </c>
       <c r="E131" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4750,10 +4507,10 @@
         <v>32.1712</v>
       </c>
       <c r="E132" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4770,10 +4527,10 @@
         <v>-0.344070107999268</v>
       </c>
       <c r="E133" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4790,10 +4547,10 @@
         <v>-0.154075599487461</v>
       </c>
       <c r="E134" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4810,10 +4567,10 @@
         <v>0.0607459271462567</v>
       </c>
       <c r="E135" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4830,10 +4587,10 @@
         <v>0.63059857221307</v>
       </c>
       <c r="E136" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4850,10 +4607,10 @@
         <v>1.19096650192202</v>
       </c>
       <c r="E137" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4870,10 +4627,10 @@
         <v>1.8042073952041</v>
       </c>
       <c r="E138" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4890,10 +4647,10 @@
         <v>2.2928381841479</v>
       </c>
       <c r="E139" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4910,10 +4667,10 @@
         <v>2.8816904631155</v>
       </c>
       <c r="E140" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4930,10 +4687,10 @@
         <v>3.89814570748673</v>
       </c>
       <c r="E141" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4950,10 +4707,10 @@
         <v>5.10717279882848</v>
       </c>
       <c r="E142" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4970,10 +4727,10 @@
         <v>1.31254896576972</v>
       </c>
       <c r="E143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4990,10 +4747,10 @@
         <v>4.06646988833974</v>
       </c>
       <c r="E144" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5010,10 +4767,10 @@
         <v>6.92988376349991</v>
       </c>
       <c r="E145" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5030,10 +4787,10 @@
         <v>14.7449487461102</v>
       </c>
       <c r="E146" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5050,10 +4807,10 @@
         <v>21.760711147721</v>
       </c>
       <c r="E147" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -5070,10 +4827,10 @@
         <v>28.6602132527915</v>
       </c>
       <c r="E148" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5090,10 +4847,10 @@
         <v>33.2366392092257</v>
       </c>
       <c r="E149" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5110,10 +4867,10 @@
         <v>38.467528830313</v>
       </c>
       <c r="E150" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5130,10 +4887,10 @@
         <v>46.4145524437122</v>
       </c>
       <c r="E151" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5150,10 +4907,10 @@
         <v>54.0704594545122</v>
       </c>
       <c r="E152" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -5170,10 +4927,10 @@
         <v>63.8925</v>
       </c>
       <c r="E153" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5190,10 +4947,10 @@
         <v>116.7507</v>
       </c>
       <c r="E154" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5210,10 +4967,10 @@
         <v>116.7816</v>
       </c>
       <c r="E155" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5230,10 +4987,10 @@
         <v>118.7167</v>
       </c>
       <c r="E156" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5250,10 +5007,10 @@
         <v>118.3199</v>
       </c>
       <c r="E157" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -5270,10 +5027,10 @@
         <v>116.4284</v>
       </c>
       <c r="E158" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -5290,10 +5047,10 @@
         <v>118.7026</v>
       </c>
       <c r="E159" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -5310,10 +5067,10 @@
         <v>118.0385</v>
       </c>
       <c r="E160" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -5330,10 +5087,10 @@
         <v>106.0066</v>
       </c>
       <c r="E161" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -5350,10 +5107,10 @@
         <v>116.9916</v>
       </c>
       <c r="E162" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -5370,10 +5127,10 @@
         <v>115.5925</v>
       </c>
       <c r="E163" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5390,10 +5147,10 @@
         <v>115.9052</v>
       </c>
       <c r="E164" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -5410,10 +5167,10 @@
         <v>115.9137</v>
       </c>
       <c r="E165" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5430,10 +5187,10 @@
         <v>114.3101</v>
       </c>
       <c r="E166" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5450,10 +5207,10 @@
         <v>116.5194</v>
       </c>
       <c r="E167" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5470,10 +5227,10 @@
         <v>115.5471</v>
       </c>
       <c r="E168" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -5490,10 +5247,10 @@
         <v>2.8946</v>
       </c>
       <c r="E169" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5510,10 +5267,10 @@
         <v>3.1367</v>
       </c>
       <c r="E170" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -5530,10 +5287,10 @@
         <v>3.3791</v>
       </c>
       <c r="E171" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5550,10 +5307,10 @@
         <v>4.095</v>
       </c>
       <c r="E172" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -5570,10 +5327,10 @@
         <v>4.7078</v>
       </c>
       <c r="E173" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5590,10 +5347,10 @@
         <v>5.2293</v>
       </c>
       <c r="E174" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -5610,10 +5367,10 @@
         <v>6.4907</v>
       </c>
       <c r="E175" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5630,10 +5387,10 @@
         <v>8.0433</v>
       </c>
       <c r="E176" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -5650,10 +5407,10 @@
         <v>0.42</v>
       </c>
       <c r="E177" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5670,10 +5427,10 @@
         <v>1.88</v>
       </c>
       <c r="E178" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -5690,10 +5447,10 @@
         <v>3.97</v>
       </c>
       <c r="E179" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5710,10 +5467,10 @@
         <v>6.24</v>
       </c>
       <c r="E180" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -5730,10 +5487,10 @@
         <v>11.46</v>
       </c>
       <c r="E181" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5750,10 +5507,10 @@
         <v>16.74</v>
       </c>
       <c r="E182" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -5770,10 +5527,10 @@
         <v>20.7</v>
       </c>
       <c r="E183" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5790,10 +5547,10 @@
         <v>0.07</v>
       </c>
       <c r="E184" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -5810,10 +5567,10 @@
         <v>0.18</v>
       </c>
       <c r="E185" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5830,10 +5587,10 @@
         <v>0.45</v>
       </c>
       <c r="E186" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -5850,10 +5607,10 @@
         <v>0.67</v>
       </c>
       <c r="E187" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -5870,10 +5627,10 @@
         <v>1.24</v>
       </c>
       <c r="E188" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -5890,10 +5647,10 @@
         <v>1.87</v>
       </c>
       <c r="E189" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -5910,10 +5667,10 @@
         <v>2.36</v>
       </c>
       <c r="E190" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -5930,10 +5687,10 @@
         <v>2.23</v>
       </c>
       <c r="E191" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -5950,10 +5707,10 @@
         <v>12.04</v>
       </c>
       <c r="E192" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -5970,10 +5727,10 @@
         <v>26.84</v>
       </c>
       <c r="E193" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -5990,10 +5747,10 @@
         <v>39.06</v>
       </c>
       <c r="E194" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -6010,10 +5767,10 @@
         <v>58.81</v>
       </c>
       <c r="E195" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -6030,10 +5787,10 @@
         <v>69.68</v>
       </c>
       <c r="E196" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -6050,10 +5807,10 @@
         <v>75.46</v>
       </c>
       <c r="E197" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -6070,10 +5827,10 @@
         <v>2.0774</v>
       </c>
       <c r="E198" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -6090,10 +5847,10 @@
         <v>5.3018</v>
       </c>
       <c r="E199" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -6110,10 +5867,10 @@
         <v>8.1563</v>
       </c>
       <c r="E200" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -6130,10 +5887,10 @@
         <v>16.1909</v>
       </c>
       <c r="E201" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -6150,10 +5907,10 @@
         <v>30.4208</v>
       </c>
       <c r="E202" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -6170,10 +5927,10 @@
         <v>43.4877</v>
       </c>
       <c r="E203" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -6190,10 +5947,10 @@
         <v>58.3095</v>
       </c>
       <c r="E204" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -6210,10 +5967,10 @@
         <v>69.2409</v>
       </c>
       <c r="E205" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -6230,10 +5987,10 @@
         <v>1.7391</v>
       </c>
       <c r="E206" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -6250,10 +6007,10 @@
         <v>2.0985</v>
       </c>
       <c r="E207" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -6270,10 +6027,10 @@
         <v>2.31</v>
       </c>
       <c r="E208" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -6290,10 +6047,10 @@
         <v>2.9126</v>
       </c>
       <c r="E209" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -6310,10 +6067,10 @@
         <v>4.0755</v>
       </c>
       <c r="E210" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -6330,10 +6087,10 @@
         <v>5.1855</v>
       </c>
       <c r="E211" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -6350,10 +6107,10 @@
         <v>6.5387</v>
       </c>
       <c r="E212" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -6370,10 +6127,10 @@
         <v>7.6382</v>
       </c>
       <c r="E213" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -6390,10 +6147,10 @@
         <v>-0.0189</v>
       </c>
       <c r="E214" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -6410,10 +6167,10 @@
         <v>-0.2459</v>
       </c>
       <c r="E215" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -6430,10 +6187,10 @@
         <v>-0.1576</v>
       </c>
       <c r="E216" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -6450,10 +6207,10 @@
         <v>0.0063</v>
       </c>
       <c r="E217" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -6470,10 +6227,10 @@
         <v>0.4099</v>
       </c>
       <c r="E218" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -6490,10 +6247,10 @@
         <v>0.9774</v>
       </c>
       <c r="E219" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -6510,10 +6267,10 @@
         <v>1.2044</v>
       </c>
       <c r="E220" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -6530,10 +6287,10 @@
         <v>1.608</v>
       </c>
       <c r="E221" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -6550,10 +6307,10 @@
         <v>2.0368</v>
       </c>
       <c r="E222" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -6570,10 +6327,10 @@
         <v>2.6044</v>
       </c>
       <c r="E223" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -6590,10 +6347,10 @@
         <v>3.2192</v>
       </c>
       <c r="E224" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -6610,10 +6367,10 @@
         <v>13.4528</v>
       </c>
       <c r="E225" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -6630,10 +6387,10 @@
         <v>23.2424</v>
       </c>
       <c r="E226" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -6650,10 +6407,10 @@
         <v>48.6785</v>
       </c>
       <c r="E227" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -6670,10 +6427,10 @@
         <v>86.008</v>
       </c>
       <c r="E228" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -6690,10 +6447,10 @@
         <v>98.6944</v>
       </c>
       <c r="E229" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -6710,10 +6467,10 @@
         <v>99.3075</v>
       </c>
       <c r="E230" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -6730,10 +6487,10 @@
         <v>100.2167</v>
       </c>
       <c r="E231" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -6750,10 +6507,10 @@
         <v>0.7597</v>
       </c>
       <c r="E232" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -6770,10 +6527,10 @@
         <v>3.4628</v>
       </c>
       <c r="E233" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -6790,10 +6547,10 @@
         <v>6.8203</v>
       </c>
       <c r="E234" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -6810,10 +6567,10 @@
         <v>17.4619</v>
       </c>
       <c r="E235" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -6830,10 +6587,10 @@
         <v>36.1702</v>
       </c>
       <c r="E236" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -6850,10 +6607,10 @@
         <v>57.6241</v>
       </c>
       <c r="E237" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -6870,10 +6627,10 @@
         <v>80.1309</v>
       </c>
       <c r="E238" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -6890,10 +6647,10 @@
         <v>100.4467</v>
       </c>
       <c r="E239" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -6910,10 +6667,10 @@
         <v>116.2953</v>
       </c>
       <c r="E240" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="241" spans="1:6">
@@ -6930,10 +6687,10 @@
         <v>55.8141</v>
       </c>
       <c r="E241" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -6950,10 +6707,10 @@
         <v>96.8029</v>
       </c>
       <c r="E242" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:6">
@@ -6970,10 +6727,10 @@
         <v>101.7341</v>
       </c>
       <c r="E243" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:6">
@@ -6990,10 +6747,10 @@
         <v>102.2891</v>
       </c>
       <c r="E244" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:6">
@@ -7010,10 +6767,10 @@
         <v>103.0962</v>
       </c>
       <c r="E245" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="246" spans="1:6">
@@ -7030,10 +6787,10 @@
         <v>99.2118</v>
       </c>
       <c r="E246" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="247" spans="1:6">
@@ -7050,10 +6807,10 @@
         <v>100.7378</v>
       </c>
       <c r="E247" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="248" spans="1:6">
@@ -7070,10 +6827,10 @@
         <v>101.6963</v>
       </c>
       <c r="E248" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="249" spans="1:6">
@@ -7090,10 +6847,10 @@
         <v>101.9107</v>
       </c>
       <c r="E249" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="250" spans="1:6">
@@ -7110,10 +6867,10 @@
         <v>101.7089</v>
       </c>
       <c r="E250" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -7130,10 +6887,10 @@
         <v>2.5743</v>
       </c>
       <c r="E251" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -7150,10 +6907,10 @@
         <v>6.9933</v>
       </c>
       <c r="E252" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -7170,10 +6927,10 @@
         <v>11.3913</v>
       </c>
       <c r="E253" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6">
@@ -7190,10 +6947,10 @@
         <v>22.9675</v>
       </c>
       <c r="E254" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="255" spans="1:6">
@@ -7210,10 +6967,10 @@
         <v>43.7943</v>
       </c>
       <c r="E255" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="256" spans="1:6">
@@ -7230,10 +6987,10 @@
         <v>62.4749</v>
       </c>
       <c r="E256" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -7250,10 +7007,10 @@
         <v>80.7538</v>
       </c>
       <c r="E257" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -7270,10 +7027,10 @@
         <v>91.0509</v>
       </c>
       <c r="E258" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -7290,10 +7047,10 @@
         <v>0.5108</v>
       </c>
       <c r="E259" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -7310,10 +7067,10 @@
         <v>0.3342</v>
       </c>
       <c r="E260" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -7330,10 +7087,10 @@
         <v>0.5612</v>
       </c>
       <c r="E261" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -7350,10 +7107,10 @@
         <v>0.8639</v>
       </c>
       <c r="E262" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -7370,10 +7127,10 @@
         <v>1.6963</v>
       </c>
       <c r="E263" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -7390,10 +7147,10 @@
         <v>2.6044</v>
       </c>
       <c r="E264" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -7410,10 +7167,10 @@
         <v>3.2223</v>
       </c>
       <c r="E265" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -7430,10 +7187,10 @@
         <v>3.9665</v>
       </c>
       <c r="E266" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -7450,10 +7207,10 @@
         <v>4.7988</v>
       </c>
       <c r="E267" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7470,10 +7227,10 @@
         <v>5.9087</v>
       </c>
       <c r="E268" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -7490,10 +7247,10 @@
         <v>43.7203</v>
       </c>
       <c r="E269" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7510,10 +7267,10 @@
         <v>93.5141</v>
       </c>
       <c r="E270" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -7530,10 +7287,10 @@
         <v>91.6112</v>
       </c>
       <c r="E271" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -7550,10 +7307,10 @@
         <v>95.8822</v>
       </c>
       <c r="E272" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -7570,10 +7327,10 @@
         <v>97.1086</v>
       </c>
       <c r="E273" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -7590,10 +7347,10 @@
         <v>96.8548</v>
       </c>
       <c r="E274" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -7610,10 +7367,10 @@
         <v>96.4954</v>
       </c>
       <c r="E275" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -7630,10 +7387,10 @@
         <v>97.5315</v>
       </c>
       <c r="E276" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -7650,10 +7407,10 @@
         <v>1.7391</v>
       </c>
       <c r="E277" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -7670,10 +7427,10 @@
         <v>2.0985</v>
       </c>
       <c r="E278" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -7690,10 +7447,10 @@
         <v>2.31</v>
       </c>
       <c r="E279" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -7710,10 +7467,10 @@
         <v>2.9126</v>
       </c>
       <c r="E280" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -7730,10 +7487,10 @@
         <v>4.0755</v>
       </c>
       <c r="E281" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -7750,10 +7507,10 @@
         <v>5.1855</v>
       </c>
       <c r="E282" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7770,10 +7527,10 @@
         <v>6.5387</v>
       </c>
       <c r="E283" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -7790,10 +7547,10 @@
         <v>7.6382</v>
       </c>
       <c r="E284" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -7810,10 +7567,10 @@
         <v>2.4157</v>
       </c>
       <c r="E285" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -7830,10 +7587,10 @@
         <v>9.0337</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -7850,10 +7607,10 @@
         <v>15.5989</v>
       </c>
       <c r="E287" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -7870,10 +7627,10 @@
         <v>32.81</v>
       </c>
       <c r="E288" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -7890,10 +7647,10 @@
         <v>62.5172</v>
       </c>
       <c r="E289" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -7910,10 +7667,10 @@
         <v>84.0311</v>
       </c>
       <c r="E290" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -7930,10 +7687,10 @@
         <v>96.2205</v>
       </c>
       <c r="E291" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -7950,10 +7707,10 @@
         <v>98.9692</v>
       </c>
       <c r="E292" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -7970,10 +7727,10 @@
         <v>6.04</v>
       </c>
       <c r="E293" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -7990,10 +7747,10 @@
         <v>40.26</v>
       </c>
       <c r="E294" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -8010,10 +7767,10 @@
         <v>81.2</v>
       </c>
       <c r="E295" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -8030,10 +7787,10 @@
         <v>96.43</v>
       </c>
       <c r="E296" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="297" spans="1:6">
@@ -8050,10 +7807,10 @@
         <v>101.55</v>
       </c>
       <c r="E297" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="298" spans="1:6">
@@ -8070,10 +7827,10 @@
         <v>101.14</v>
       </c>
       <c r="E298" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:6">
@@ -8090,10 +7847,10 @@
         <v>101.55</v>
       </c>
       <c r="E299" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="300" spans="1:6">
@@ -8110,10 +7867,10 @@
         <v>0.02</v>
       </c>
       <c r="E300" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="301" spans="1:6">
@@ -8130,10 +7887,10 @@
         <v>0.68</v>
       </c>
       <c r="E301" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="302" spans="1:6">
@@ -8150,10 +7907,10 @@
         <v>3.22</v>
       </c>
       <c r="E302" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="303" spans="1:6">
@@ -8170,10 +7927,10 @@
         <v>5.83</v>
       </c>
       <c r="E303" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304" spans="1:6">
@@ -8190,10 +7947,10 @@
         <v>11.67</v>
       </c>
       <c r="E304" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="305" spans="1:6">
@@ -8210,10 +7967,10 @@
         <v>17.41</v>
       </c>
       <c r="E305" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="306" spans="1:6">
@@ -8230,10 +7987,10 @@
         <v>22.34</v>
       </c>
       <c r="E306" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="307" spans="1:6">
@@ -8250,10 +8007,10 @@
         <v>43.7203</v>
       </c>
       <c r="E307" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308" spans="1:6">
@@ -8270,10 +8027,10 @@
         <v>93.5141</v>
       </c>
       <c r="E308" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="309" spans="1:6">
@@ -8290,10 +8047,10 @@
         <v>91.6112</v>
       </c>
       <c r="E309" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="310" spans="1:6">
@@ -8310,10 +8067,10 @@
         <v>95.8822</v>
       </c>
       <c r="E310" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -8330,10 +8087,10 @@
         <v>97.1086</v>
       </c>
       <c r="E311" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="312" spans="1:6">
@@ -8350,10 +8107,10 @@
         <v>96.8548</v>
       </c>
       <c r="E312" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="313" spans="1:6">
@@ -8370,10 +8127,10 @@
         <v>96.4954</v>
       </c>
       <c r="E313" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="314" spans="1:6">
@@ -8390,10 +8147,10 @@
         <v>97.5315</v>
       </c>
       <c r="E314" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -8410,10 +8167,10 @@
         <v>0.1072</v>
       </c>
       <c r="E315" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -8430,10 +8187,10 @@
         <v>6.7915</v>
       </c>
       <c r="E316" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -8450,10 +8207,10 @@
         <v>14.6109</v>
       </c>
       <c r="E317" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -8470,10 +8227,10 @@
         <v>22.2916</v>
       </c>
       <c r="E318" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -8490,10 +8247,10 @@
         <v>37.9808</v>
       </c>
       <c r="E319" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -8510,10 +8267,10 @@
         <v>48.8145</v>
       </c>
       <c r="E320" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -8530,10 +8287,10 @@
         <v>55.9781</v>
       </c>
       <c r="E321" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -8550,10 +8307,10 @@
         <v>61.0228</v>
       </c>
       <c r="E322" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -8570,10 +8327,10 @@
         <v>65.9415</v>
       </c>
       <c r="E323" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -8590,10 +8347,10 @@
         <v>70.4566</v>
       </c>
       <c r="E324" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -8610,10 +8367,10 @@
         <v>23.0988</v>
       </c>
       <c r="E325" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -8630,10 +8387,10 @@
         <v>72.651</v>
       </c>
       <c r="E326" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -8650,10 +8407,10 @@
         <v>74.0888</v>
       </c>
       <c r="E327" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -8670,10 +8427,10 @@
         <v>74.3915</v>
       </c>
       <c r="E328" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -8690,10 +8447,10 @@
         <v>74.8581</v>
       </c>
       <c r="E329" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -8710,10 +8467,10 @@
         <v>73.1051</v>
       </c>
       <c r="E330" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -8730,10 +8487,10 @@
         <v>73.3447</v>
       </c>
       <c r="E331" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -8750,10 +8507,10 @@
         <v>73.6348</v>
       </c>
       <c r="E332" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -8770,10 +8527,10 @@
         <v>73.6095</v>
       </c>
       <c r="E333" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -8790,10 +8547,10 @@
         <v>73.3951</v>
       </c>
       <c r="E334" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
